--- a/output/pdf_financials_xlsx/ZON.xlsx
+++ b/output/pdf_financials_xlsx/ZON.xlsx
@@ -1279,16 +1279,16 @@
         <v>0.55353</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.508646</v>
+        <v>-0.508646</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.332171</v>
+        <v>-0.332171</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.593919</v>
+        <v>-0.593919</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.58334</v>
+        <v>-0.58334</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-0.156981</v>
@@ -1297,7 +1297,7 @@
         <v>0.08595700000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.484991</v>
+        <v>-0.484991</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-0.811732</v>
@@ -1334,7 +1334,7 @@
         <v>-0.03</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.10706</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1570,25 +1570,25 @@
         <v>-0.624631</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.445696</v>
+        <v>-0.445696</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.394358</v>
+        <v>-0.394358</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.55353</v>
+        <v>-0.55353</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.508646</v>
+        <v>-0.508646</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.332171</v>
+        <v>-0.332171</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.593919</v>
+        <v>-0.593919</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.58334</v>
+        <v>-0.58334</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-0.156981</v>
@@ -1597,7 +1597,7 @@
         <v>0.08595700000000001</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.484991</v>
+        <v>-0.484991</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-0.811732</v>
@@ -1744,25 +1744,25 @@
         <v>-0.624631</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.445696</v>
+        <v>-0.445696</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.394358</v>
+        <v>-0.394358</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.55353</v>
+        <v>-0.55353</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.508646</v>
+        <v>-0.508646</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.332171</v>
+        <v>-0.332171</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.593919</v>
+        <v>-0.593919</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.58334</v>
+        <v>-0.58334</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-0.156981</v>
@@ -1771,7 +1771,7 @@
         <v>0.08595700000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.484991</v>
+        <v>-0.484991</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-0.811732</v>
@@ -1918,16 +1918,16 @@
         <v>15.615775</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>22.2848</v>
+        <v>-22.2848</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>19.7179</v>
+        <v>-19.7179</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>27.6765</v>
+        <v>-27.6765</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>25.4323</v>
+        <v>-25.4323</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2005,16 +2005,16 @@
         <v>0.55353</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.508646</v>
+        <v>-0.508646</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.332171</v>
+        <v>-0.332171</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.593919</v>
+        <v>-0.593919</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.58334</v>
+        <v>-0.58334</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.156981</v>
@@ -2023,7 +2023,7 @@
         <v>0.08595700000000001</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.484991</v>
+        <v>-0.484991</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-0.811732</v>
@@ -2121,16 +2121,16 @@
         <v>0.5579460000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.513062</v>
+        <v>-0.50423</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.333094</v>
+        <v>-0.331248</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.595755</v>
+        <v>-0.592083</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.588624</v>
+        <v>-0.578056</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.147678</v>
@@ -2139,7 +2139,7 @@
         <v>0.09426900000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.493303</v>
+        <v>-0.476679</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-0.8034210000000001</v>
@@ -2268,19 +2268,19 @@
         <v>7.069502636924484</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -2289,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-0</v>
@@ -34878,10 +34878,10 @@
         </is>
       </c>
       <c r="Q271" s="5" t="n">
-        <v>0.484991</v>
+        <v>-0.484991</v>
       </c>
       <c r="R271" s="5" t="n">
-        <v>0.811732</v>
+        <v>-0.811732</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -36763,28 +36763,28 @@
         <v>-0.624631</v>
       </c>
       <c r="H291" s="5" t="n">
-        <v>0.445696</v>
+        <v>-0.445696</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>0.394358</v>
+        <v>-0.394358</v>
       </c>
       <c r="J291" s="5" t="n">
-        <v>0.55353</v>
+        <v>-0.55353</v>
       </c>
       <c r="K291" s="5" t="n">
-        <v>0.508646</v>
+        <v>-0.508646</v>
       </c>
       <c r="L291" s="5" t="n">
-        <v>0.332171</v>
+        <v>-0.332171</v>
       </c>
       <c r="M291" s="5" t="n">
-        <v>0.593919</v>
+        <v>-0.593919</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>0.58334</v>
+        <v>-0.58334</v>
       </c>
       <c r="O291" s="5" t="n">
-        <v>0.156981</v>
+        <v>-0.156981</v>
       </c>
       <c r="P291" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ZON.xlsx
+++ b/output/pdf_financials_xlsx/ZON.xlsx
@@ -1035,49 +1035,49 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004176</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00457</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002185</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00032</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000597</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.00013</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.004136</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001757</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.02042</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.015435</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000268</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.00281</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.024517</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.012154</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.002388</v>
       </c>
     </row>
     <row r="13">
@@ -1993,49 +1993,49 @@
         <v>-0.399321</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.628684</v>
+        <v>-0.63286</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.489447</v>
+        <v>0.484877</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.424358</v>
+        <v>0.422173</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.55353</v>
+        <v>0.55321</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.508646</v>
+        <v>-0.509243</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.332171</v>
+        <v>-0.332301</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.593919</v>
+        <v>-0.598055</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.58334</v>
+        <v>-0.585097</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.156981</v>
+        <v>-0.177401</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.08595700000000001</v>
+        <v>0.070522</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.484991</v>
+        <v>-0.485259</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.811732</v>
+        <v>-0.814542</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.06386600000000001</v>
+        <v>-0.088383</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.487713</v>
+        <v>-0.499867</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.325319</v>
+        <v>-0.327707</v>
       </c>
     </row>
     <row r="28">
@@ -2109,49 +2109,49 @@
         <v>-0.397723</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.623326</v>
+        <v>-0.627502</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.495318</v>
+        <v>0.490748</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.430177</v>
+        <v>0.427992</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.5579460000000001</v>
+        <v>0.557626</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.50423</v>
+        <v>-0.504827</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.331248</v>
+        <v>-0.331378</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.592083</v>
+        <v>-0.5962190000000001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.578056</v>
+        <v>-0.579813</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.147678</v>
+        <v>-0.168098</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.09426900000000001</v>
+        <v>0.078834</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.476679</v>
+        <v>-0.476947</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.8034210000000001</v>
+        <v>-0.806231</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.05754</v>
+        <v>-0.082057</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.487223</v>
+        <v>-0.499377</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.325319</v>
+        <v>-0.327707</v>
       </c>
     </row>
     <row r="30">
@@ -7805,22 +7805,22 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000491</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000714</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.00079</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000969</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000969</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000259</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -7863,22 +7863,22 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000491</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000714</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.00079</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000969</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000969</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000259</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>0</v>
@@ -24173,7 +24173,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -25981,7 +25985,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -29983,7 +29991,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -34319,7 +34327,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -35798,7 +35806,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -35885,7 +35893,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">

--- a/output/pdf_financials_xlsx/ZON.xlsx
+++ b/output/pdf_financials_xlsx/ZON.xlsx
@@ -1285,22 +1285,22 @@
         <v>-0.332171</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.593919</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.58334</v>
+        <v>0.025129</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.156981</v>
+        <v>-0.573076</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.08595700000000001</v>
+        <v>-0.166135</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.484991</v>
+        <v>0</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-0.811732</v>
+        <v>0.001313</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-0.06386600000000001</v>
@@ -1343,22 +1343,22 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.593919</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.608469</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>0.416095</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>0.252092</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.484991</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.813045</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -2011,22 +2011,22 @@
         <v>-0.332301</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.598055</v>
+        <v>-0.004136</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.585097</v>
+        <v>0.023372</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.177401</v>
+        <v>-0.593496</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.070522</v>
+        <v>-0.18157</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.485259</v>
+        <v>-0.000268</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.814542</v>
+        <v>-0.001497</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.088383</v>
@@ -2127,22 +2127,22 @@
         <v>-0.331378</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.5962190000000001</v>
+        <v>-0.0023</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.579813</v>
+        <v>0.028656</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.168098</v>
+        <v>-0.584193</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.078834</v>
+        <v>-0.173258</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.476947</v>
+        <v>0.008044000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.806231</v>
+        <v>0.006814</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.082057</v>
@@ -2276,23 +2276,27 @@
       <c r="I31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>-0</v>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>2421.381670579808</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-72.60729815940643</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-151.7392482017636</v>
+      </c>
+      <c r="N31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>61922.69611576543</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -3723,40 +3727,40 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>0.021128</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.025228</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.025228</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>0.028269</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>0.028269</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>0.028269</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>0.028724</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>0.035018</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>0.071758</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>0.07657600000000001</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>0.07657600000000001</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>0.07657600000000001</v>
       </c>
       <c r="O56" s="3" t="n">
         <v>0</v>
@@ -3781,40 +3785,40 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.001598</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.006957</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.012828</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.018647</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>0.023063</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>0.027479</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>0.028402</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>0.030238</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>0.035522</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>0.044825</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>0.053137</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>0.061449</v>
       </c>
       <c r="O57" s="3" t="n">
         <v>0</v>
@@ -4246,49 +4250,49 @@
         <v>0.08708100000000001</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.01342</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.00147</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.022853</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.010547</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.00572</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.039503</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.06801</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.07865</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.128512</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.020743</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.02985</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.062201</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.051629</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.025258</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.018637</v>
       </c>
     </row>
     <row r="65">
@@ -4414,55 +4418,55 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.01986</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.01479</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.02916</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.01685</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.019735</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.019737</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.019737</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.024848</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.025919</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.042286</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.010404</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.019837</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.033793</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.037406</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.041741</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.04908</v>
       </c>
     </row>
     <row r="68">
@@ -7016,22 +7020,22 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>-0.003772</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>-0.003772</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>-0.078178</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>-0.017667</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>-0.009926000000000001</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>-0.007744</v>
       </c>
     </row>
     <row r="111">
@@ -18986,7 +18990,11 @@
           <t>Gain on revaluation of long-term amounts due to related parties, net of accretion expense (note 17)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -20760,7 +20768,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -20954,7 +20966,11 @@
           <t>Gain on revaluation of long-term amounts due to related parties, net of accretion expense (note 16)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -21360,7 +21376,11 @@
           <t>Gain on revaluation of long-term amounts due to related parties, net of accretion expense (note 18)</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -34622,7 +34642,11 @@
           <t>Loss before deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -34719,7 +34743,11 @@
           <t>Deferred income tax recovery (note 10)</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -35224,7 +35252,11 @@
           <t>Deferred income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -36166,7 +36198,11 @@
           <t>Loss before deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -36263,7 +36299,11 @@
           <t>Deferred income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -37037,7 +37077,11 @@
           <t>Loss before income tax (recovery)</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -37136,7 +37180,11 @@
           <t>Deferred income tax (recovery) (note 13)</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
